--- a/karta-rutiny.xlsx
+++ b/karta-rutiny.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t xml:space="preserve">ЛЮМЕН · КАРТА РУТИНЫ</t>
   </si>
@@ -62,7 +62,10 @@
     <t xml:space="preserve">3.  В трёх последних колонках выбери «да» или «нет» из выпадающего списка.</t>
   </si>
   <si>
-    <t xml:space="preserve">Заполняешь только колонки B, C, D, F, G, H (они подсвечены). Колонки E, I, J, K считаются сами — не трогай их.</t>
+    <t xml:space="preserve">     Третий признак — не про важность задачи. Важно всё. Он про то, увидишь ли ты ошибку до того, как результат уйдёт дальше:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     черновик письма ты прочитаешь перед отправкой, а цифра, уехавшая в отчёт, всплывёт через месяц.</t>
   </si>
   <si>
     <t xml:space="preserve">№</t>
@@ -86,7 +89,7 @@
     <t xml:space="preserve">Есть готовый образец</t>
   </si>
   <si>
-    <t xml:space="preserve">Ошибка не критична</t>
+    <t xml:space="preserve">Ошибку видно до отправки</t>
   </si>
   <si>
     <t xml:space="preserve">Баллов</t>
@@ -162,6 +165,21 @@
   </si>
   <si>
     <t xml:space="preserve">Одна задача, сделанная до конца, полезнее трёх настроенных наполовину.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Примеры формулировок, если не идёт:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">отвечаю на письма по статусу заказа  ·  собираю недельную сводку для руководителя  ·  пишу текст вакансии и разбираю отклики</t>
+  </si>
+  <si>
+    <t xml:space="preserve">свожу отчёт по расходам  ·  составляю ТЗ подрядчику  ·  веду протокол планёрки и рассылаю задачи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">отвечаю на типовые вопросы клиентов в чате  ·  сверяю договор с нашим шаблоном  ·  готовлю КП по запросу</t>
+  </si>
+  <si>
+    <t xml:space="preserve">заполняю карточки товара  ·  перевожу переписку с поставщиком  ·  готовлю справку по клиенту перед встречей</t>
   </si>
 </sst>
 </file>
@@ -754,7 +772,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -803,39 +821,44 @@
         <v>6</v>
       </c>
     </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -843,7 +866,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>30</v>
@@ -856,20 +879,20 @@
         <v>10.825</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I11" s="12" t="n">
         <f aca="false">IF($B11="",0,COUNTIF($F11:$H11,"да"))</f>
         <v>3</v>
       </c>
       <c r="J11" s="13" t="str">
-        <f aca="false">IF($B11="","",IF($I11=3,"Отдавай сегодня",IF($I11&lt;=1,"Пока не трогай",IF($G11&lt;&gt;"да","Сначала сделай образец",IF($H11&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B11="","",IF($I11=3,"Отдавай сегодня",IF($I11&lt;=1,"Пока не трогай",IF($G11&lt;&gt;"да","Сначала сделай образец",IF($H11&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v>Отдавай сегодня</v>
       </c>
       <c r="K11" s="14" t="n">
@@ -896,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="13" t="str">
-        <f aca="false">IF($B12="","",IF($I12=3,"Отдавай сегодня",IF($I12&lt;=1,"Пока не трогай",IF($G12&lt;&gt;"да","Сначала сделай образец",IF($H12&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B12="","",IF($I12=3,"Отдавай сегодня",IF($I12&lt;=1,"Пока не трогай",IF($G12&lt;&gt;"да","Сначала сделай образец",IF($H12&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K12" s="14" t="n">
@@ -923,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="13" t="str">
-        <f aca="false">IF($B13="","",IF($I13=3,"Отдавай сегодня",IF($I13&lt;=1,"Пока не трогай",IF($G13&lt;&gt;"да","Сначала сделай образец",IF($H13&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B13="","",IF($I13=3,"Отдавай сегодня",IF($I13&lt;=1,"Пока не трогай",IF($G13&lt;&gt;"да","Сначала сделай образец",IF($H13&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K13" s="14" t="n">
@@ -950,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="13" t="str">
-        <f aca="false">IF($B14="","",IF($I14=3,"Отдавай сегодня",IF($I14&lt;=1,"Пока не трогай",IF($G14&lt;&gt;"да","Сначала сделай образец",IF($H14&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B14="","",IF($I14=3,"Отдавай сегодня",IF($I14&lt;=1,"Пока не трогай",IF($G14&lt;&gt;"да","Сначала сделай образец",IF($H14&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K14" s="14" t="n">
@@ -977,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="13" t="str">
-        <f aca="false">IF($B15="","",IF($I15=3,"Отдавай сегодня",IF($I15&lt;=1,"Пока не трогай",IF($G15&lt;&gt;"да","Сначала сделай образец",IF($H15&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B15="","",IF($I15=3,"Отдавай сегодня",IF($I15&lt;=1,"Пока не трогай",IF($G15&lt;&gt;"да","Сначала сделай образец",IF($H15&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K15" s="14" t="n">
@@ -1004,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="13" t="str">
-        <f aca="false">IF($B16="","",IF($I16=3,"Отдавай сегодня",IF($I16&lt;=1,"Пока не трогай",IF($G16&lt;&gt;"да","Сначала сделай образец",IF($H16&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B16="","",IF($I16=3,"Отдавай сегодня",IF($I16&lt;=1,"Пока не трогай",IF($G16&lt;&gt;"да","Сначала сделай образец",IF($H16&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K16" s="14" t="n">
@@ -1031,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="13" t="str">
-        <f aca="false">IF($B17="","",IF($I17=3,"Отдавай сегодня",IF($I17&lt;=1,"Пока не трогай",IF($G17&lt;&gt;"да","Сначала сделай образец",IF($H17&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B17="","",IF($I17=3,"Отдавай сегодня",IF($I17&lt;=1,"Пока не трогай",IF($G17&lt;&gt;"да","Сначала сделай образец",IF($H17&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K17" s="14" t="n">
@@ -1058,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="13" t="str">
-        <f aca="false">IF($B18="","",IF($I18=3,"Отдавай сегодня",IF($I18&lt;=1,"Пока не трогай",IF($G18&lt;&gt;"да","Сначала сделай образец",IF($H18&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B18="","",IF($I18=3,"Отдавай сегодня",IF($I18&lt;=1,"Пока не трогай",IF($G18&lt;&gt;"да","Сначала сделай образец",IF($H18&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K18" s="14" t="n">
@@ -1085,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="13" t="str">
-        <f aca="false">IF($B19="","",IF($I19=3,"Отдавай сегодня",IF($I19&lt;=1,"Пока не трогай",IF($G19&lt;&gt;"да","Сначала сделай образец",IF($H19&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B19="","",IF($I19=3,"Отдавай сегодня",IF($I19&lt;=1,"Пока не трогай",IF($G19&lt;&gt;"да","Сначала сделай образец",IF($H19&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K19" s="14" t="n">
@@ -1112,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="13" t="str">
-        <f aca="false">IF($B20="","",IF($I20=3,"Отдавай сегодня",IF($I20&lt;=1,"Пока не трогай",IF($G20&lt;&gt;"да","Сначала сделай образец",IF($H20&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B20="","",IF($I20=3,"Отдавай сегодня",IF($I20&lt;=1,"Пока не трогай",IF($G20&lt;&gt;"да","Сначала сделай образец",IF($H20&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K20" s="14" t="n">
@@ -1139,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="13" t="str">
-        <f aca="false">IF($B21="","",IF($I21=3,"Отдавай сегодня",IF($I21&lt;=1,"Пока не трогай",IF($G21&lt;&gt;"да","Сначала сделай образец",IF($H21&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B21="","",IF($I21=3,"Отдавай сегодня",IF($I21&lt;=1,"Пока не трогай",IF($G21&lt;&gt;"да","Сначала сделай образец",IF($H21&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K21" s="14" t="n">
@@ -1166,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="13" t="str">
-        <f aca="false">IF($B22="","",IF($I22=3,"Отдавай сегодня",IF($I22&lt;=1,"Пока не трогай",IF($G22&lt;&gt;"да","Сначала сделай образец",IF($H22&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B22="","",IF($I22=3,"Отдавай сегодня",IF($I22&lt;=1,"Пока не трогай",IF($G22&lt;&gt;"да","Сначала сделай образец",IF($H22&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K22" s="14" t="n">
@@ -1193,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="13" t="str">
-        <f aca="false">IF($B23="","",IF($I23=3,"Отдавай сегодня",IF($I23&lt;=1,"Пока не трогай",IF($G23&lt;&gt;"да","Сначала сделай образец",IF($H23&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B23="","",IF($I23=3,"Отдавай сегодня",IF($I23&lt;=1,"Пока не трогай",IF($G23&lt;&gt;"да","Сначала сделай образец",IF($H23&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K23" s="14" t="n">
@@ -1220,7 +1243,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="13" t="str">
-        <f aca="false">IF($B24="","",IF($I24=3,"Отдавай сегодня",IF($I24&lt;=1,"Пока не трогай",IF($G24&lt;&gt;"да","Сначала сделай образец",IF($H24&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B24="","",IF($I24=3,"Отдавай сегодня",IF($I24&lt;=1,"Пока не трогай",IF($G24&lt;&gt;"да","Сначала сделай образец",IF($H24&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K24" s="14" t="n">
@@ -1247,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="13" t="str">
-        <f aca="false">IF($B25="","",IF($I25=3,"Отдавай сегодня",IF($I25&lt;=1,"Пока не трогай",IF($G25&lt;&gt;"да","Сначала сделай образец",IF($H25&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B25="","",IF($I25=3,"Отдавай сегодня",IF($I25&lt;=1,"Пока не трогай",IF($G25&lt;&gt;"да","Сначала сделай образец",IF($H25&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K25" s="14" t="n">
@@ -1274,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="13" t="str">
-        <f aca="false">IF($B26="","",IF($I26=3,"Отдавай сегодня",IF($I26&lt;=1,"Пока не трогай",IF($G26&lt;&gt;"да","Сначала сделай образец",IF($H26&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B26="","",IF($I26=3,"Отдавай сегодня",IF($I26&lt;=1,"Пока не трогай",IF($G26&lt;&gt;"да","Сначала сделай образец",IF($H26&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K26" s="14" t="n">
@@ -1301,7 +1324,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="13" t="str">
-        <f aca="false">IF($B27="","",IF($I27=3,"Отдавай сегодня",IF($I27&lt;=1,"Пока не трогай",IF($G27&lt;&gt;"да","Сначала сделай образец",IF($H27&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B27="","",IF($I27=3,"Отдавай сегодня",IF($I27&lt;=1,"Пока не трогай",IF($G27&lt;&gt;"да","Сначала сделай образец",IF($H27&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K27" s="14" t="n">
@@ -1328,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="13" t="str">
-        <f aca="false">IF($B28="","",IF($I28=3,"Отдавай сегодня",IF($I28&lt;=1,"Пока не трогай",IF($G28&lt;&gt;"да","Сначала сделай образец",IF($H28&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B28="","",IF($I28=3,"Отдавай сегодня",IF($I28&lt;=1,"Пока не трогай",IF($G28&lt;&gt;"да","Сначала сделай образец",IF($H28&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K28" s="14" t="n">
@@ -1355,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="13" t="str">
-        <f aca="false">IF($B29="","",IF($I29=3,"Отдавай сегодня",IF($I29&lt;=1,"Пока не трогай",IF($G29&lt;&gt;"да","Сначала сделай образец",IF($H29&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B29="","",IF($I29=3,"Отдавай сегодня",IF($I29&lt;=1,"Пока не трогай",IF($G29&lt;&gt;"да","Сначала сделай образец",IF($H29&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K29" s="14" t="n">
@@ -1382,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="13" t="str">
-        <f aca="false">IF($B30="","",IF($I30=3,"Отдавай сегодня",IF($I30&lt;=1,"Пока не трогай",IF($G30&lt;&gt;"да","Сначала сделай образец",IF($H30&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B30="","",IF($I30=3,"Отдавай сегодня",IF($I30&lt;=1,"Пока не трогай",IF($G30&lt;&gt;"да","Сначала сделай образец",IF($H30&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K30" s="14" t="n">
@@ -1409,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="13" t="str">
-        <f aca="false">IF($B31="","",IF($I31=3,"Отдавай сегодня",IF($I31&lt;=1,"Пока не трогай",IF($G31&lt;&gt;"да","Сначала сделай образец",IF($H31&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B31="","",IF($I31=3,"Отдавай сегодня",IF($I31&lt;=1,"Пока не трогай",IF($G31&lt;&gt;"да","Сначала сделай образец",IF($H31&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K31" s="14" t="n">
@@ -1436,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="13" t="str">
-        <f aca="false">IF($B32="","",IF($I32=3,"Отдавай сегодня",IF($I32&lt;=1,"Пока не трогай",IF($G32&lt;&gt;"да","Сначала сделай образец",IF($H32&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B32="","",IF($I32=3,"Отдавай сегодня",IF($I32&lt;=1,"Пока не трогай",IF($G32&lt;&gt;"да","Сначала сделай образец",IF($H32&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K32" s="14" t="n">
@@ -1463,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="13" t="str">
-        <f aca="false">IF($B33="","",IF($I33=3,"Отдавай сегодня",IF($I33&lt;=1,"Пока не трогай",IF($G33&lt;&gt;"да","Сначала сделай образец",IF($H33&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B33="","",IF($I33=3,"Отдавай сегодня",IF($I33&lt;=1,"Пока не трогай",IF($G33&lt;&gt;"да","Сначала сделай образец",IF($H33&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K33" s="14" t="n">
@@ -1490,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="13" t="str">
-        <f aca="false">IF($B34="","",IF($I34=3,"Отдавай сегодня",IF($I34&lt;=1,"Пока не трогай",IF($G34&lt;&gt;"да","Сначала сделай образец",IF($H34&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B34="","",IF($I34=3,"Отдавай сегодня",IF($I34&lt;=1,"Пока не трогай",IF($G34&lt;&gt;"да","Сначала сделай образец",IF($H34&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K34" s="14" t="n">
@@ -1517,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="13" t="str">
-        <f aca="false">IF($B35="","",IF($I35=3,"Отдавай сегодня",IF($I35&lt;=1,"Пока не трогай",IF($G35&lt;&gt;"да","Сначала сделай образец",IF($H35&lt;&gt;"да","Только черновик, проверять целиком","Разово — да, настраивать — нет")))))</f>
+        <f aca="false">IF($B35="","",IF($I35=3,"Отдавай сегодня",IF($I35&lt;=1,"Пока не трогай",IF($G35&lt;&gt;"да","Сначала сделай образец",IF($H35&lt;&gt;"да","Отдавай только проверяемую часть","Разово — да, настраивать — нет")))))</f>
         <v/>
       </c>
       <c r="K35" s="14" t="n">
@@ -1527,7 +1550,7 @@
     </row>
     <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B37" s="18"/>
       <c r="C37" s="18"/>
@@ -1542,7 +1565,7 @@
     </row>
     <row r="38" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B38" s="19"/>
       <c r="C38" s="19"/>
@@ -1552,7 +1575,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G38" s="21"/>
       <c r="H38" s="21"/>
@@ -1562,7 +1585,7 @@
     </row>
     <row r="39" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B39" s="19"/>
       <c r="C39" s="19"/>
@@ -1572,7 +1595,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G39" s="21"/>
       <c r="H39" s="21"/>
@@ -1582,7 +1605,7 @@
     </row>
     <row r="40" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B40" s="19"/>
       <c r="C40" s="19"/>
@@ -1592,7 +1615,7 @@
         <v>10.825</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G40" s="21"/>
       <c r="H40" s="21"/>
@@ -1602,7 +1625,7 @@
     </row>
     <row r="41" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
@@ -1612,7 +1635,7 @@
         <v>7.5775</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G41" s="21"/>
       <c r="H41" s="21"/>
@@ -1622,7 +1645,7 @@
     </row>
     <row r="42" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
@@ -1632,7 +1655,7 @@
         <v>0.9471875</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G42" s="21"/>
       <c r="H42" s="21"/>
@@ -1642,17 +1665,17 @@
     </row>
     <row r="43" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B43" s="19"/>
       <c r="C43" s="19"/>
       <c r="D43" s="19"/>
       <c r="E43" s="22" t="n">
-        <f aca="false">SUMPRODUCT((($J$11:$J$35="Сначала сделай образец")+($J$11:$J$35="Только черновик, проверять целиком"))*$E$11:$E$35)*0.45</f>
+        <f aca="false">SUMPRODUCT((($J$11:$J$35="Сначала сделай образец")+($J$11:$J$35="Отдавай только проверяемую часть"))*$E$11:$E$35)*0.45</f>
         <v>0</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G43" s="21"/>
       <c r="H43" s="21"/>
@@ -1662,27 +1685,27 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1690,12 +1713,40 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="26" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="26"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="26" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/karta-rutiny.xlsx
+++ b/karta-rutiny.xlsx
@@ -9,6 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="Карта рутины" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Примеры" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="95">
   <si>
     <t xml:space="preserve">ЛЮМЕН · КАРТА РУТИНЫ</t>
   </si>
@@ -180,6 +181,210 @@
   </si>
   <si>
     <t xml:space="preserve">заполняю карточки товара  ·  перевожу переписку с поставщиком  ·  готовлю справку по клиенту перед встречей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЧТО ЗНАЧИТ «ОТДАТЬ ЗАДАЧУ» — ДЕСЯТЬ ПРИМЕРОВ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Запросы можно копировать как есть, подставив своё. Устроены они одинаково, и это главное: сначала образец, потом факты, потом прямой запрет додумывать.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Без первого получается вода, без третьего — выдуманные цифры.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Группа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Готовый запрос — скопируй и подставь своё</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Себе оставляешь</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Письма клиентам по статусу заказа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">отдавай сегодня</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Один раз собери пять своих прошлых писем на похожую тему — это образец тона.
+2. Вставь запрос ниже, подставив свои письма. Сохрани его: дальше меняешь только факты.
+3. Проверь цифры и даты, отправь.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ниже пять моих писем клиентам. Изучи, как я пишу: длину, тон, как здороваюсь и прощаюсь, как подаю плохие новости.
+[вставить письма]
+Теперь напиши письмо тем же тоном. Факты: заказ №1234, задержка пять дней, причина — таможенное оформление. Предложи клиенту два варианта: ждать целиком или забрать готовую часть сейчас. Не извиняйся дважды. Закончи вопросом.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проверить факты и отправить.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Недельная сводка руководителю</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Выгрузи данные за неделю как есть — таблицей, списком, хоть скриншотом.
+2. Приложи прошлую сводку как образец структуры.
+3. Расставь акценты сама: что здесь важно, а что шум.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вот моя сводка за прошлую неделю — используй её структуру и стиль как образец:
+[вставить сводку]
+Вот данные за эту неделю:
+[вставить данные]
+Собери сводку в том же формате. Числа бери только из данных: ничего не считай сам и не додумывай. Если для раздела данных нет — напиши «нет данных», а не пропускай раздел.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Решить, что вынести наверх.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разбор откликов на вакансию</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Сформулируй три-четыре критерия одной строкой — только измеримые.
+2. Вставь отклики пачкой, пронумерованными.
+3. Решение по каждому кандидату принимаешь сама.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Критерии: опыт в закупках от двух лет, английский от B1, готовность работать из офиса в Москве.
+Ниже отклики, каждый под своим номером:
+[вставить отклики]
+Разбей их на три группы: подходит, под вопросом, не подходит. Для каждого — одна строка почему, со ссылкой на конкретный критерий. Личные качества не оценивай, только соответствие критериям.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выбор кандидатов. ИИ сортирует, а не отбирает.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отчёт по расходам за месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">только проверяемая часть</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Числа не отдавай вообще. Отдай структуру и формулировки.
+2. Проси заготовку, а не расчёт.
+3. Числа подставляешь сама, в своей таблице.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вот структура моего отчёта по расходам: [перечислить разделы].
+Вот комментарии, которые я обычно пишу к отклонениям: [два-три примера].
+Собери шаблон отчёта на этот месяц: разделы в том же порядке, пустые поля под числа и заготовки комментариев для трёх случаев — отклонение вверх, отклонение вниз, без изменений.
+Никаких числовых значений не подставляй и не выдумывай, оставь пропуски.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Все числа до единого.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Техническое задание подрядчику</t>
+  </si>
+  <si>
+    <t xml:space="preserve">нужен образец</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Нет удачного прошлого ТЗ — напиши одно руками и сохрани. Это разовая работа.
+2. Дальше каждый раз используешь запрос ниже.
+3. Сроки, бюджет и приёмку заполняешь сама.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вот моё ТЗ, по которому подрядчик всё сделал правильно с первого раза. Разбери его структуру:
+[вставить ТЗ]
+Теперь по той же структуре собери ТЗ для новой задачи. Задача своими словами:
+[описать задачу]
+Поля «сроки», «бюджет» и «критерии приёмки» оставь пустыми. В конце дай список вопросов, которые подрядчик задаст, если в задаче чего-то не хватает.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сроки, бюджет, критерии приёмки.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Протокол планёрки и задачи по итогам</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Включи запись на телефоне или пиши заметки как обычно.
+2. Расшифровку целиком отдай в чат вместе с запросом ниже.
+3. Проверь, что никого не забыли, и разошли.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вот расшифровка планёрки:
+[вставить текст]
+Сделай протокол из трёх частей:
+1. Решения — что решили, по одной строке на решение.
+2. Задачи — что, кто, к какому сроку, если срок называли.
+3. Вопросы без ответа — что обсуждали, но не решили.
+Ничего не додумывай. Если ответственный не назван — пиши «не назначен», если срока нет — «срок не назван».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проверить полноту и разослать.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Типовые вопросы клиентов в чате</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Собери двадцать своих прошлых ответов — чем разнообразнее, тем лучше.
+2. Вставь запрос ниже один раз и сохрани как шаблон.
+3. Всё про цены и сроки дописываешь руками.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ниже двадцать моих ответов клиентам. Изучи тон и уровень подробности:
+[вставить ответы]
+Дальше отвечай на новые вопросы так же. Жёсткое правило: если в вопросе есть цена, срок или обязательство — не отвечай, а напиши «нужен ответ менеджера». На всё остальное отвечай сам.
+Первый вопрос: [вопрос клиента]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Всё, где есть цена, срок или обязательство.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сверка договора с вашим шаблоном</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Оба текста целиком в чат.
+2. Проси список различий, а не оценку.
+3. Существенность расхождений оцениваешь сама.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Первый текст — наш стандартный шаблон договора:
+[вставить шаблон]
+Второй — версия, которую прислал контрагент:
+[вставить версию]
+Найди все различия и выпиши таблицей: пункт, было, стало, тип изменения (добавлено, удалено, переформулировано).
+Не оценивай, выгодно это нам или нет, — только фиксируй. Изменения в нумерации и опечатки вынеси отдельным списком в конец.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вывод, что из этого существенно.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коммерческое предложение по запросу</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Сохрани одно своё КП, после которого клиент согласился.
+2. Дальше каждый раз запрос ниже.
+3. Ставки и условия проставляешь руками, всегда.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вот КП, после которого клиент согласился. Это образец структуры и тона:
+[вставить КП]
+Новый запрос клиента:
+[вставить запрос]
+Собери КП по той же структуре. Все цены, ставки и сроки оставь как [___] — подставлю сама. Если в запросе клиента не хватает данных для расчёта, перечисли в конце, что нужно уточнить.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ставки, условия, сроки.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Справка по клиенту перед встречей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Скопируй переписку за год и список заказов.
+2. Вставь запрос ниже.
+3. Что предложить на встрече — решаешь сама.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вот переписка с клиентом за год и список его заказов:
+[вставить материалы]
+Сделай справку на одну страницу к встрече: чем занимается компания, что заказывали и как часто, о чём договаривались в прошлый раз, какие были шероховатости и чем закончились, какие темы клиент поднимал сам.
+Только факты из материалов. Если чего-то в них нет — так и напиши, не достраивай.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Что предложить.</t>
   </si>
 </sst>
 </file>
@@ -193,7 +398,7 @@
     <numFmt numFmtId="167" formatCode="0;;\—"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,8 +525,24 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF0E6B62"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF16232B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -331,13 +552,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE3E7DE"/>
-        <bgColor rgb="FFD6E5E1"/>
+        <bgColor rgb="FFE8EAE4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF6C9"/>
-        <bgColor rgb="FFFFFDF2"/>
+        <bgColor rgb="FFF2E6D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -350,6 +571,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF16232B"/>
         <bgColor rgb="FF003300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E5E1"/>
+        <bgColor rgb="FFE3E7DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2E6D0"/>
+        <bgColor rgb="FFE8EAE4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EAE4"/>
+        <bgColor rgb="FFE3E7DE"/>
       </patternFill>
     </fill>
   </fills>
@@ -402,7 +641,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -509,6 +748,38 @@
     </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -550,11 +821,11 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF6C9"/>
-      <rgbColor rgb="FFE3E7DE"/>
+      <rgbColor rgb="FFE8EAE4"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFFFFDF2"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -564,9 +835,9 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFFFFDF2"/>
+      <rgbColor rgb="FFE3E7DE"/>
       <rgbColor rgb="FFD6E5E1"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFF2E6D0"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -1785,4 +2056,232 @@
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="27" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="117" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="117" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="117" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/karta-rutiny.xlsx
+++ b/karta-rutiny.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="123">
   <si>
     <t xml:space="preserve">ЛЮМЕН · КАРТА РУТИНЫ</t>
   </si>
@@ -183,7 +183,7 @@
     <t xml:space="preserve">заполняю карточки товара  ·  перевожу переписку с поставщиком  ·  готовлю справку по клиенту перед встречей</t>
   </si>
   <si>
-    <t xml:space="preserve">ЧТО ЗНАЧИТ «ОТДАТЬ ЗАДАЧУ» — ДЕСЯТЬ ПРИМЕРОВ</t>
+    <t xml:space="preserve">ЧТО ЗНАЧИТ «ОТДАТЬ ЗАДАЧУ» — ШЕСТНАДЦАТЬ ПРИМЕРОВ</t>
   </si>
   <si>
     <t xml:space="preserve">Запросы можно копировать как есть, подставив своё. Устроены они одинаково, и это главное: сначала образец, потом факты, потом прямой запрет додумывать.</t>
@@ -192,6 +192,9 @@
     <t xml:space="preserve">Без первого получается вода, без третьего — выдуманные цифры.</t>
   </si>
   <si>
+    <t xml:space="preserve">Профессия</t>
+  </si>
+  <si>
     <t xml:space="preserve">Группа</t>
   </si>
   <si>
@@ -202,6 +205,9 @@
   </si>
   <si>
     <t xml:space="preserve">Письма клиентам по статусу заказа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">офис и продажи</t>
   </si>
   <si>
     <t xml:space="preserve">отдавай сегодня</t>
@@ -385,6 +391,115 @@
   </si>
   <si>
     <t xml:space="preserve">Что предложить.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заметки после сессии</t>
+  </si>
+  <si>
+    <t xml:space="preserve">психологи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Обезличь текст до того, как что-то куда-то вставишь: клиент — «К.», без города, профессии, названий компаний и узнаваемых деталей.
+2. Отдавай структурирование, а не интерпретацию.
+3. Готовый текст перечитай и допиши то, что не стала отдавать.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вот моя заметка после сессии. Она обезличена: клиент обозначен как «К.», узнаваемые детали убраны.
+[вставить заметку]
+Приведи её к моей обычной структуре: запрос, что происходило в сессии, гипотезы, план на следующую.
+Ничего не интерпретируй сверх написанного, не добавляй диагнозов и не делай выводов, которых в тексте нет. Если чего-то для раздела не хватает — так и напиши.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Всё, по чему человека можно узнать, и любые клинические выводы.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ответы на первые обращения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Собери пятнадцать своих прошлых ответов на «здравствуйте, а вы работаете с…».
+2. Вставь запрос ниже, сохрани как шаблон.
+3. Решение, брать ли человека в работу, принимаешь сама.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ниже пятнадцать моих ответов на первые обращения. Изучи тон: тёплый, но без обещаний результата.
+[вставить ответы]
+Отвечай так же на новые обращения. Жёсткие правила: не обещай результат и сроки терапии, не ставь и не предполагай диагнозов, на вопрос о стоимости отвечай моей формулировкой из образцов.
+Первое обращение: [текст обращения]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Решение, твой ли это клиент.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Материалы клиенту между сессиями</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Возьми одну свою удачную раздатку — по ней видно стиль и уровень подробности.
+2. Дальше каждый раз запрос ниже.
+3. Проверь, подходит ли это конкретному человеку.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вот раздатка, которую я обычно даю клиентам. По ней видно мой стиль и уровень подробности:
+[вставить образец]
+Сделай такую же на тему [тема] для взрослого человека без психологического образования.
+Без терминов, которые не объяснены тут же. Без обещаний, что станет легче. В конце — три вопроса для самонаблюдения между сессиями.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Решение, кому это давать, а кому рано.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Домашние задания под уровень ученика</t>
+  </si>
+  <si>
+    <t xml:space="preserve">репетиторы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Возьми задание, которое хорошо зашло ученикам этого уровня, — это эталон сложности.
+2. Проси ответы отдельным блоком, чтобы ученику отдать только условия.
+3. Перерешай каждый ответ сама.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вот задание, которое я обычно даю ученикам этого уровня:
+[вставить задание]
+Сделай ещё пять такой же сложности на тему [тема]. Уровень строго как в образце — не усложняй.
+Ответы вынеси отдельным блоком в конце, чтобы я могла отдать ученику только условия.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проверку решений. В вычислениях он ошибается чаще, чем кажется, — перерешай всё.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отчёт родителям о прогрессе</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Собери два прошлых отчёта как образец структуры и тона.
+2. Приложи свои заметки по ученику за месяц.
+3. Оценки и прогнозы ставишь сама.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вот мои прошлые отчёты родителям — по ним видно структуру и тон:
+[вставить отчёты]
+Вот мои заметки по ученику за месяц:
+[вставить заметки]
+Собери отчёт в том же формате. Только факты из заметок, ничего не додумывай. Не обещай результата к экзамену и не давай прогнозов по баллам.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценки, прогнозы и всё, что звучит как обещание.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">План занятия на новую тему</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Сохрани один свой план, по которому занятие прошло удачно.
+2. Дальше запрос ниже под каждую новую тему.
+3. Конкретные упражнения подбираешь под ученика.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вот мой план занятия, по которому всё прошло удачно:
+[вставить план]
+Сделай по той же структуре план на тему [тема] для ученика [класс или уровень]. Раздели на блоки с таймингом, как в образце.
+Упражнения бери типовые — я заменю на свои там, где не подойдёт. В конце добавь список типичных ошибок по этой теме, чтобы я знала, где притормозить.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подбор упражнений под конкретного ученика.</t>
   </si>
 </sst>
 </file>
@@ -762,12 +877,12 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2063,14 +2178,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2096,183 +2212,336 @@
         <v>49</v>
       </c>
       <c r="C5" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="28" t="s">
         <v>17</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>50</v>
       </c>
       <c r="E5" s="28" t="s">
         <v>51</v>
       </c>
+      <c r="F5" s="28" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="31" t="s">
         <v>56</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="29" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="31" t="s">
         <v>60</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="117" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="29" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="31" t="s">
         <v>64</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="31" t="s">
         <v>67</v>
       </c>
+      <c r="B9" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>68</v>
+      </c>
       <c r="D9" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" s="31" t="s">
         <v>69</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="31" t="s">
         <v>72</v>
       </c>
+      <c r="B10" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>73</v>
+      </c>
       <c r="D10" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" s="31" t="s">
         <v>74</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="29" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="31" t="s">
         <v>78</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="117" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="31" t="s">
         <v>82</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>68</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" s="31" t="s">
         <v>86</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>73</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" s="31" t="s">
         <v>90</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="117" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="E15" s="31" t="s">
         <v>94</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="117" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="117" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="117" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="F18" s="30" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="117" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="117" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
